--- a/public/samples/remains/phutungdungcu.xlsx
+++ b/public/samples/remains/phutungdungcu.xlsx
@@ -1,31 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/leanhtu/Desktop/merge/project_freelance/KHO/Kho còn lại/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB66D4B0-5C7F-5C4B-8506-156262410E27}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="960" windowWidth="27640" windowHeight="15440" xr2:uid="{CF52CC2E-CB8D-0F40-8691-5E1DC7E3DA19}"/>
+    <workbookView windowWidth="28800" windowHeight="12040"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="120">
   <si>
     <t>Tồn</t>
   </si>
@@ -49,6 +38,9 @@
   </si>
   <si>
     <t>Date</t>
+  </si>
+  <si>
+    <t>Đơn giá</t>
   </si>
   <si>
     <t>CD0001</t>
@@ -387,29 +379,370 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="d&quot;/&quot;m&quot;/&quot;yyyy"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="6">
+    <numFmt numFmtId="176" formatCode="d&quot;/&quot;m&quot;/&quot;yyyy"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="21">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -417,27 +750,313 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="60% - Accent6" xfId="1" builtinId="52"/>
+    <cellStyle name="40% - Accent6" xfId="2" builtinId="51"/>
+    <cellStyle name="60% - Accent5" xfId="3" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="4" builtinId="49"/>
+    <cellStyle name="40% - Accent5" xfId="5" builtinId="47"/>
+    <cellStyle name="20% - Accent5" xfId="6" builtinId="46"/>
+    <cellStyle name="60% - Accent4" xfId="7" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="8" builtinId="45"/>
+    <cellStyle name="40% - Accent4" xfId="9" builtinId="43"/>
+    <cellStyle name="Accent4" xfId="10" builtinId="41"/>
+    <cellStyle name="Linked Cell" xfId="11" builtinId="24"/>
+    <cellStyle name="40% - Accent3" xfId="12" builtinId="39"/>
+    <cellStyle name="60% - Accent2" xfId="13" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="14" builtinId="37"/>
+    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
+    <cellStyle name="20% - Accent2" xfId="16" builtinId="34"/>
+    <cellStyle name="Accent2" xfId="17" builtinId="33"/>
+    <cellStyle name="40% - Accent1" xfId="18" builtinId="31"/>
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30"/>
+    <cellStyle name="Accent1" xfId="20" builtinId="29"/>
+    <cellStyle name="Neutral" xfId="21" builtinId="28"/>
+    <cellStyle name="60% - Accent1" xfId="22" builtinId="32"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="20% - Accent4" xfId="24" builtinId="42"/>
+    <cellStyle name="Total" xfId="25" builtinId="25"/>
+    <cellStyle name="Output" xfId="26" builtinId="21"/>
+    <cellStyle name="Currency" xfId="27" builtinId="4"/>
+    <cellStyle name="20% - Accent3" xfId="28" builtinId="38"/>
+    <cellStyle name="Note" xfId="29" builtinId="10"/>
+    <cellStyle name="Input" xfId="30" builtinId="20"/>
+    <cellStyle name="Heading 4" xfId="31" builtinId="19"/>
+    <cellStyle name="Calculation" xfId="32" builtinId="22"/>
+    <cellStyle name="Good" xfId="33" builtinId="26"/>
+    <cellStyle name="Heading 3" xfId="34" builtinId="18"/>
+    <cellStyle name="CExplanatory Text" xfId="35" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="36" builtinId="16"/>
+    <cellStyle name="Comma [0]" xfId="37" builtinId="6"/>
+    <cellStyle name="20% - Accent6" xfId="38" builtinId="50"/>
+    <cellStyle name="Title" xfId="39" builtinId="15"/>
+    <cellStyle name="Currency [0]" xfId="40" builtinId="7"/>
+    <cellStyle name="Warning Text" xfId="41" builtinId="11"/>
+    <cellStyle name="Followed Hyperlink" xfId="42" builtinId="9"/>
+    <cellStyle name="Heading 2" xfId="43" builtinId="17"/>
+    <cellStyle name="Comma" xfId="44" builtinId="3"/>
+    <cellStyle name="Check Cell" xfId="45" builtinId="23"/>
+    <cellStyle name="60% - Accent3" xfId="46" builtinId="40"/>
+    <cellStyle name="Percent" xfId="47" builtinId="5"/>
+    <cellStyle name="Hyperlink" xfId="48" builtinId="8"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -486,7 +1105,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -519,26 +1138,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -571,23 +1173,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -729,31 +1314,26 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FFF8A39-3443-6849-8BC0-8EB8A280C4F3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I56"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.8"/>
   <cols>
     <col min="3" max="3" width="19.5" customWidth="1"/>
-    <col min="5" max="5" width="19.1640625" customWidth="1"/>
+    <col min="5" max="5" width="19.1617647058824" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="7:8">
       <c r="G1" s="2"/>
       <c r="H1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -778,143 +1358,145 @@
       <c r="H2" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="1"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I2" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="C3" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="2">
+        <v>44927</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3" s="3"/>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="2">
-        <v>44927</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3" s="1"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="2">
+        <v>44927</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4" s="3"/>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="2">
-        <v>44927</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4" s="1"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="2">
+        <v>44927</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5" s="3"/>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="2">
-        <v>44927</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5" s="1"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="2">
+        <v>44927</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6" s="3"/>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="2">
-        <v>44927</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6" s="1"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="2">
+        <v>44927</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7" s="3"/>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="G7" s="2">
-        <v>44927</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7" s="1"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="D8">
         <v>4</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G8" s="2">
         <v>44927</v>
@@ -922,23 +1504,23 @@
       <c r="H8">
         <v>4</v>
       </c>
-      <c r="I8" s="1"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I8" s="3"/>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>10</v>
+        <v>24</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="D9">
         <v>2</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G9" s="2">
         <v>44927</v>
@@ -946,119 +1528,119 @@
       <c r="H9">
         <v>2</v>
       </c>
-      <c r="I9" s="1"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I9" s="3"/>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>10</v>
+        <v>26</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="2">
+        <v>44927</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10" s="3"/>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G10" s="2">
-        <v>44927</v>
-      </c>
-      <c r="H10">
-        <v>1</v>
-      </c>
-      <c r="I10" s="1"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="D11">
         <v>1</v>
       </c>
       <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="2">
+        <v>44927</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11" s="3"/>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G11" s="2">
-        <v>44927</v>
-      </c>
-      <c r="H11">
-        <v>1</v>
-      </c>
-      <c r="I11" s="1"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="D12">
         <v>1</v>
       </c>
       <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="2">
+        <v>44927</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12" s="3"/>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G12" s="2">
-        <v>44927</v>
-      </c>
-      <c r="H12">
-        <v>1</v>
-      </c>
-      <c r="I12" s="1"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="D13">
         <v>1</v>
       </c>
       <c r="F13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="2">
+        <v>44927</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13" s="3"/>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="G13" s="2">
-        <v>44927</v>
-      </c>
-      <c r="H13">
-        <v>1</v>
-      </c>
-      <c r="I13" s="1"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="D14">
         <v>50</v>
       </c>
       <c r="F14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G14" s="2">
         <v>44927</v>
@@ -1066,143 +1648,143 @@
       <c r="H14">
         <v>50</v>
       </c>
-      <c r="I14" s="1"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I14" s="3"/>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>10</v>
+        <v>36</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="D15">
         <v>1</v>
       </c>
       <c r="F15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="2">
+        <v>44927</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15" s="3"/>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G15" s="2">
-        <v>44927</v>
-      </c>
-      <c r="H15">
-        <v>1</v>
-      </c>
-      <c r="I15" s="1"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="D16">
         <v>1</v>
       </c>
       <c r="F16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" s="2">
+        <v>44927</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16" s="3"/>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G16" s="2">
-        <v>44927</v>
-      </c>
-      <c r="H16">
-        <v>1</v>
-      </c>
-      <c r="I16" s="1"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="D17">
         <v>1</v>
       </c>
       <c r="F17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" s="2">
+        <v>44927</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17" s="3"/>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G17" s="2">
-        <v>44927</v>
-      </c>
-      <c r="H17">
-        <v>1</v>
-      </c>
-      <c r="I17" s="1"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>40</v>
-      </c>
-      <c r="B18" t="s">
-        <v>41</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="D18">
         <v>1</v>
       </c>
       <c r="F18" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18" s="2">
+        <v>44927</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18" s="3"/>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G18" s="2">
-        <v>44927</v>
-      </c>
-      <c r="H18">
-        <v>1</v>
-      </c>
-      <c r="I18" s="1"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>42</v>
-      </c>
-      <c r="B19" t="s">
-        <v>43</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="D19">
         <v>1</v>
       </c>
       <c r="F19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" s="2">
+        <v>44927</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19" s="3"/>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G19" s="2">
-        <v>44927</v>
-      </c>
-      <c r="H19">
-        <v>1</v>
-      </c>
-      <c r="I19" s="1"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>44</v>
-      </c>
-      <c r="B20" t="s">
-        <v>45</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="D20">
         <v>1</v>
       </c>
       <c r="F20" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G20" s="2">
         <v>44927</v>
@@ -1210,23 +1792,23 @@
       <c r="H20">
         <v>1</v>
       </c>
-      <c r="I20" s="1"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I20" s="3"/>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B21" t="s">
-        <v>47</v>
-      </c>
-      <c r="C21" s="3" t="s">
         <v>48</v>
       </c>
+      <c r="C21" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="D21">
         <v>1</v>
       </c>
       <c r="F21" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G21" s="2">
         <v>44927</v>
@@ -1234,23 +1816,23 @@
       <c r="H21">
         <v>1</v>
       </c>
-      <c r="I21" s="1"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I21" s="3"/>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B22" t="s">
-        <v>50</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="D22">
         <v>5</v>
       </c>
       <c r="F22" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G22" s="2">
         <v>44927</v>
@@ -1258,23 +1840,23 @@
       <c r="H22">
         <v>5</v>
       </c>
-      <c r="I22" s="1"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I22" s="3"/>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B23" t="s">
-        <v>52</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>48</v>
+        <v>53</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="D23">
         <v>3</v>
       </c>
       <c r="F23" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G23" s="2">
         <v>44927</v>
@@ -1282,23 +1864,23 @@
       <c r="H23">
         <v>3</v>
       </c>
-      <c r="I23" s="1"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I23" s="3"/>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B24" t="s">
-        <v>54</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="D24">
         <v>5</v>
       </c>
       <c r="F24" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G24" s="2">
         <v>44927</v>
@@ -1306,23 +1888,23 @@
       <c r="H24">
         <v>5</v>
       </c>
-      <c r="I24" s="1"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I24" s="3"/>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B25" t="s">
-        <v>56</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>48</v>
+        <v>57</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="D25">
         <v>100</v>
       </c>
       <c r="F25" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G25" s="2">
         <v>44927</v>
@@ -1330,23 +1912,23 @@
       <c r="H25">
         <v>100</v>
       </c>
-      <c r="I25" s="1"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I25" s="3"/>
+    </row>
+    <row r="26" spans="1:9">
       <c r="A26" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B26" t="s">
-        <v>58</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>48</v>
+        <v>59</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="D26">
         <v>20</v>
       </c>
       <c r="F26" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G26" s="2">
         <v>44927</v>
@@ -1354,23 +1936,23 @@
       <c r="H26">
         <v>20</v>
       </c>
-      <c r="I26" s="1"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I26" s="3"/>
+    </row>
+    <row r="27" spans="1:9">
       <c r="A27" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B27" t="s">
-        <v>60</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="D27">
         <v>4</v>
       </c>
       <c r="F27" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G27" s="2">
         <v>44927</v>
@@ -1378,23 +1960,23 @@
       <c r="H27">
         <v>4</v>
       </c>
-      <c r="I27" s="1"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I27" s="3"/>
+    </row>
+    <row r="28" spans="1:9">
       <c r="A28" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B28" t="s">
-        <v>62</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>48</v>
+        <v>63</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="D28">
         <v>2</v>
       </c>
       <c r="F28" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G28" s="2">
         <v>44927</v>
@@ -1402,23 +1984,23 @@
       <c r="H28">
         <v>2</v>
       </c>
-      <c r="I28" s="1"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I28" s="3"/>
+    </row>
+    <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B29" t="s">
-        <v>64</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>48</v>
+        <v>65</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="D29">
         <v>2</v>
       </c>
       <c r="F29" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G29" s="2">
         <v>44927</v>
@@ -1426,23 +2008,23 @@
       <c r="H29">
         <v>2</v>
       </c>
-      <c r="I29" s="1"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I29" s="3"/>
+    </row>
+    <row r="30" spans="1:9">
       <c r="A30" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B30" t="s">
-        <v>66</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>48</v>
+        <v>67</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="D30">
         <v>3</v>
       </c>
       <c r="F30" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G30" s="2">
         <v>44927</v>
@@ -1450,23 +2032,23 @@
       <c r="H30">
         <v>3</v>
       </c>
-      <c r="I30" s="1"/>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I30" s="3"/>
+    </row>
+    <row r="31" spans="1:9">
       <c r="A31" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B31" t="s">
-        <v>68</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>48</v>
+        <v>69</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="D31">
         <v>3</v>
       </c>
       <c r="F31" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G31" s="2">
         <v>44927</v>
@@ -1474,23 +2056,23 @@
       <c r="H31">
         <v>3</v>
       </c>
-      <c r="I31" s="1"/>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I31" s="3"/>
+    </row>
+    <row r="32" spans="1:9">
       <c r="A32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B32" t="s">
-        <v>70</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>48</v>
+        <v>71</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="D32">
         <v>15</v>
       </c>
       <c r="F32" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G32" s="2">
         <v>44927</v>
@@ -1498,23 +2080,23 @@
       <c r="H32">
         <v>15</v>
       </c>
-      <c r="I32" s="1"/>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I32" s="3"/>
+    </row>
+    <row r="33" spans="1:9">
       <c r="A33" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B33" t="s">
-        <v>72</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>48</v>
+        <v>73</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="D33">
         <v>4</v>
       </c>
       <c r="F33" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G33" s="2">
         <v>44927</v>
@@ -1522,23 +2104,23 @@
       <c r="H33">
         <v>4</v>
       </c>
-      <c r="I33" s="1"/>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I33" s="3"/>
+    </row>
+    <row r="34" spans="1:9">
       <c r="A34" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B34" t="s">
-        <v>74</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>48</v>
+        <v>75</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="D34">
         <v>80</v>
       </c>
       <c r="F34" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G34" s="2">
         <v>44927</v>
@@ -1546,23 +2128,23 @@
       <c r="H34">
         <v>80</v>
       </c>
-      <c r="I34" s="1"/>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I34" s="3"/>
+    </row>
+    <row r="35" spans="1:9">
       <c r="A35" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B35" t="s">
-        <v>76</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>48</v>
+        <v>77</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="D35">
         <v>100</v>
       </c>
       <c r="F35" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G35" s="2">
         <v>44927</v>
@@ -1570,23 +2152,23 @@
       <c r="H35">
         <v>100</v>
       </c>
-      <c r="I35" s="1"/>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I35" s="3"/>
+    </row>
+    <row r="36" spans="1:9">
       <c r="A36" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B36" t="s">
-        <v>78</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>48</v>
+        <v>79</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="D36">
         <v>5</v>
       </c>
       <c r="F36" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G36" s="2">
         <v>44927</v>
@@ -1594,23 +2176,23 @@
       <c r="H36">
         <v>5</v>
       </c>
-      <c r="I36" s="1"/>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I36" s="3"/>
+    </row>
+    <row r="37" spans="1:9">
       <c r="A37" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B37" t="s">
-        <v>80</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>48</v>
+        <v>81</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="D37">
         <v>5</v>
       </c>
       <c r="F37" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G37" s="2">
         <v>44927</v>
@@ -1618,23 +2200,23 @@
       <c r="H37">
         <v>5</v>
       </c>
-      <c r="I37" s="1"/>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I37" s="3"/>
+    </row>
+    <row r="38" spans="1:9">
       <c r="A38" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B38" t="s">
-        <v>82</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>48</v>
+        <v>83</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="D38">
         <v>40</v>
       </c>
       <c r="F38" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G38" s="2">
         <v>44927</v>
@@ -1642,23 +2224,23 @@
       <c r="H38">
         <v>40</v>
       </c>
-      <c r="I38" s="1"/>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I38" s="3"/>
+    </row>
+    <row r="39" spans="1:9">
       <c r="A39" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B39" t="s">
-        <v>84</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>48</v>
+        <v>85</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="D39">
         <v>1</v>
       </c>
       <c r="F39" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G39" s="2">
         <v>44927</v>
@@ -1666,23 +2248,23 @@
       <c r="H39">
         <v>1</v>
       </c>
-      <c r="I39" s="1"/>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I39" s="3"/>
+    </row>
+    <row r="40" spans="1:9">
       <c r="A40" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B40" t="s">
-        <v>86</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>48</v>
+        <v>87</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="D40">
         <v>5</v>
       </c>
       <c r="F40" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G40" s="2">
         <v>44927</v>
@@ -1690,23 +2272,23 @@
       <c r="H40">
         <v>5</v>
       </c>
-      <c r="I40" s="1"/>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I40" s="3"/>
+    </row>
+    <row r="41" spans="1:9">
       <c r="A41" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B41" t="s">
-        <v>88</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>48</v>
+        <v>89</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="D41">
         <v>5</v>
       </c>
       <c r="F41" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G41" s="2">
         <v>44927</v>
@@ -1714,23 +2296,23 @@
       <c r="H41">
         <v>5</v>
       </c>
-      <c r="I41" s="1"/>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I41" s="3"/>
+    </row>
+    <row r="42" spans="1:9">
       <c r="A42" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B42" t="s">
-        <v>90</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>48</v>
+        <v>91</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="D42">
         <v>5</v>
       </c>
       <c r="F42" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G42" s="2">
         <v>44927</v>
@@ -1738,23 +2320,23 @@
       <c r="H42">
         <v>5</v>
       </c>
-      <c r="I42" s="1"/>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I42" s="3"/>
+    </row>
+    <row r="43" spans="1:9">
       <c r="A43" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B43" t="s">
-        <v>92</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>48</v>
+        <v>93</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="D43">
         <v>2</v>
       </c>
       <c r="F43" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G43" s="2">
         <v>44927</v>
@@ -1762,23 +2344,23 @@
       <c r="H43">
         <v>2</v>
       </c>
-      <c r="I43" s="1"/>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I43" s="3"/>
+    </row>
+    <row r="44" spans="1:9">
       <c r="A44" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B44" t="s">
-        <v>94</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>48</v>
+        <v>95</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="D44">
         <v>2</v>
       </c>
       <c r="F44" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G44" s="2">
         <v>44927</v>
@@ -1786,23 +2368,23 @@
       <c r="H44">
         <v>2</v>
       </c>
-      <c r="I44" s="1"/>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I44" s="3"/>
+    </row>
+    <row r="45" spans="1:9">
       <c r="A45" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B45" t="s">
-        <v>96</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>48</v>
+        <v>97</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="D45">
         <v>3</v>
       </c>
       <c r="F45" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G45" s="2">
         <v>44927</v>
@@ -1810,23 +2392,23 @@
       <c r="H45">
         <v>3</v>
       </c>
-      <c r="I45" s="1"/>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I45" s="3"/>
+    </row>
+    <row r="46" spans="1:9">
       <c r="A46" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B46" t="s">
-        <v>98</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>48</v>
+        <v>99</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="D46">
         <v>2</v>
       </c>
       <c r="F46" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G46" s="2">
         <v>44927</v>
@@ -1834,23 +2416,23 @@
       <c r="H46">
         <v>2</v>
       </c>
-      <c r="I46" s="1"/>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I46" s="3"/>
+    </row>
+    <row r="47" spans="1:9">
       <c r="A47" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B47" t="s">
-        <v>100</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>48</v>
+        <v>101</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="D47">
         <v>2</v>
       </c>
       <c r="F47" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G47" s="2">
         <v>44927</v>
@@ -1858,23 +2440,23 @@
       <c r="H47">
         <v>2</v>
       </c>
-      <c r="I47" s="1"/>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I47" s="3"/>
+    </row>
+    <row r="48" spans="1:9">
       <c r="A48" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B48" t="s">
-        <v>102</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>48</v>
+        <v>103</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="D48">
         <v>1</v>
       </c>
       <c r="F48" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G48" s="2">
         <v>44927</v>
@@ -1882,23 +2464,23 @@
       <c r="H48">
         <v>1</v>
       </c>
-      <c r="I48" s="1"/>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I48" s="3"/>
+    </row>
+    <row r="49" spans="1:9">
       <c r="A49" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B49" t="s">
-        <v>104</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>48</v>
+        <v>105</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="D49">
         <v>1</v>
       </c>
       <c r="F49" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G49" s="2">
         <v>44927</v>
@@ -1906,23 +2488,23 @@
       <c r="H49">
         <v>1</v>
       </c>
-      <c r="I49" s="1"/>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I49" s="3"/>
+    </row>
+    <row r="50" spans="1:9">
       <c r="A50" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B50" t="s">
-        <v>106</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>48</v>
+        <v>107</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="D50">
         <v>2</v>
       </c>
       <c r="F50" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G50" s="2">
         <v>44927</v>
@@ -1930,23 +2512,23 @@
       <c r="H50">
         <v>2</v>
       </c>
-      <c r="I50" s="1"/>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I50" s="3"/>
+    </row>
+    <row r="51" spans="1:9">
       <c r="A51" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B51" t="s">
-        <v>108</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>48</v>
+        <v>109</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="D51">
         <v>1</v>
       </c>
       <c r="F51" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G51" s="2">
         <v>44927</v>
@@ -1954,23 +2536,23 @@
       <c r="H51">
         <v>1</v>
       </c>
-      <c r="I51" s="1"/>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I51" s="3"/>
+    </row>
+    <row r="52" spans="1:9">
       <c r="A52" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B52" t="s">
-        <v>110</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>48</v>
+        <v>111</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="D52">
         <v>1</v>
       </c>
       <c r="F52" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G52" s="2">
         <v>44927</v>
@@ -1978,23 +2560,23 @@
       <c r="H52">
         <v>1</v>
       </c>
-      <c r="I52" s="1"/>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I52" s="3"/>
+    </row>
+    <row r="53" spans="1:9">
       <c r="A53" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B53" t="s">
-        <v>112</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>48</v>
+        <v>113</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="D53">
         <v>1</v>
       </c>
       <c r="F53" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G53" s="2">
         <v>44927</v>
@@ -2002,23 +2584,23 @@
       <c r="H53">
         <v>1</v>
       </c>
-      <c r="I53" s="1"/>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I53" s="3"/>
+    </row>
+    <row r="54" spans="1:9">
       <c r="A54" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B54" t="s">
-        <v>114</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>48</v>
+        <v>115</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="D54">
         <v>5</v>
       </c>
       <c r="F54" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G54" s="2">
         <v>44927</v>
@@ -2026,23 +2608,23 @@
       <c r="H54">
         <v>5</v>
       </c>
-      <c r="I54" s="1"/>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I54" s="3"/>
+    </row>
+    <row r="55" spans="1:9">
       <c r="A55" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B55" t="s">
-        <v>116</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>48</v>
+        <v>117</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="D55">
         <v>2</v>
       </c>
       <c r="F55" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G55" s="2">
         <v>44927</v>
@@ -2050,23 +2632,23 @@
       <c r="H55">
         <v>2</v>
       </c>
-      <c r="I55" s="1"/>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I55" s="3"/>
+    </row>
+    <row r="56" spans="1:9">
       <c r="A56" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B56" t="s">
-        <v>118</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>48</v>
+        <v>119</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="D56">
         <v>6</v>
       </c>
       <c r="F56" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G56" s="2">
         <v>44927</v>
@@ -2074,9 +2656,10 @@
       <c r="H56">
         <v>6</v>
       </c>
-      <c r="I56" s="1"/>
+      <c r="I56" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>